--- a/Pemindah JD adaptif V6/TemplateJobDescBaruKosongan/Template GOL 123_Spesialis.xlsx
+++ b/Pemindah JD adaptif V6/TemplateJobDescBaruKosongan/Template GOL 123_Spesialis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\titipan Feli\PROYEK GEDE\Database\Template Baru kosong\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\z\TemplateJobDescBaruKosongan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1034A615-3408-4336-92DE-CF4D04EE2587}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FE79A2-72B0-4293-B831-C23572947B42}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" xr2:uid="{B4CA32BC-DA9F-4539-8D41-F96D4CBDAEFA}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="54">
   <si>
     <t>JOB DESCRIPTION</t>
   </si>
@@ -147,9 +147,6 @@
     <t>JOB SPEC</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>DivisionName</t>
   </si>
   <si>
@@ -189,16 +186,10 @@
     <t>Corporate Culture PT. XYZ</t>
   </si>
   <si>
-    <t>1.</t>
-  </si>
-  <si>
     <t>ExternalXYZConnection</t>
   </si>
   <si>
-    <t>2.</t>
-  </si>
-  <si>
-    <t>3.</t>
+    <t>ExternalConnection</t>
   </si>
 </sst>
 </file>
@@ -637,7 +628,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="198">
+  <cellXfs count="201">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1012,9 +1003,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
@@ -1105,6 +1093,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1138,15 +1147,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1186,17 +1186,17 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1677,182 +1677,182 @@
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="5"/>
-      <c r="M2" s="167" t="s">
+      <c r="M2" s="173" t="s">
         <v>0</v>
       </c>
-      <c r="N2" s="168"/>
-      <c r="O2" s="168"/>
-      <c r="P2" s="168"/>
-      <c r="Q2" s="168"/>
-      <c r="R2" s="168"/>
-      <c r="S2" s="168"/>
-      <c r="T2" s="168"/>
-      <c r="U2" s="168"/>
-      <c r="V2" s="168"/>
-      <c r="W2" s="168"/>
-      <c r="X2" s="168"/>
-      <c r="Y2" s="168"/>
-      <c r="Z2" s="168"/>
-      <c r="AA2" s="168"/>
-      <c r="AB2" s="168"/>
-      <c r="AC2" s="168"/>
-      <c r="AD2" s="168"/>
-      <c r="AE2" s="168"/>
-      <c r="AF2" s="168"/>
-      <c r="AG2" s="168"/>
-      <c r="AH2" s="168"/>
-      <c r="AI2" s="168"/>
-      <c r="AJ2" s="168"/>
-      <c r="AK2" s="168"/>
-      <c r="AL2" s="168"/>
-      <c r="AM2" s="168"/>
-      <c r="AN2" s="168"/>
-      <c r="AO2" s="169"/>
-      <c r="AP2" s="143"/>
-      <c r="AQ2" s="144" t="s">
+      <c r="N2" s="174"/>
+      <c r="O2" s="174"/>
+      <c r="P2" s="174"/>
+      <c r="Q2" s="174"/>
+      <c r="R2" s="174"/>
+      <c r="S2" s="174"/>
+      <c r="T2" s="174"/>
+      <c r="U2" s="174"/>
+      <c r="V2" s="174"/>
+      <c r="W2" s="174"/>
+      <c r="X2" s="174"/>
+      <c r="Y2" s="174"/>
+      <c r="Z2" s="174"/>
+      <c r="AA2" s="174"/>
+      <c r="AB2" s="174"/>
+      <c r="AC2" s="174"/>
+      <c r="AD2" s="174"/>
+      <c r="AE2" s="174"/>
+      <c r="AF2" s="174"/>
+      <c r="AG2" s="174"/>
+      <c r="AH2" s="174"/>
+      <c r="AI2" s="174"/>
+      <c r="AJ2" s="174"/>
+      <c r="AK2" s="174"/>
+      <c r="AL2" s="174"/>
+      <c r="AM2" s="174"/>
+      <c r="AN2" s="174"/>
+      <c r="AO2" s="175"/>
+      <c r="AP2" s="142"/>
+      <c r="AQ2" s="143" t="s">
         <v>1</v>
       </c>
-      <c r="AR2" s="144"/>
-      <c r="AS2" s="144"/>
-      <c r="AT2" s="144"/>
-      <c r="AU2" s="144"/>
-      <c r="AV2" s="145" t="s">
+      <c r="AR2" s="143"/>
+      <c r="AS2" s="143"/>
+      <c r="AT2" s="143"/>
+      <c r="AU2" s="143"/>
+      <c r="AV2" s="144" t="s">
         <v>2</v>
       </c>
-      <c r="AW2" s="145" t="s">
-        <v>40</v>
-      </c>
-      <c r="AX2" s="144"/>
-      <c r="AY2" s="144"/>
-      <c r="AZ2" s="144"/>
-      <c r="BA2" s="144"/>
-      <c r="BB2" s="144"/>
-      <c r="BC2" s="144"/>
-      <c r="BD2" s="144"/>
-      <c r="BE2" s="144"/>
-      <c r="BF2" s="144"/>
-      <c r="BG2" s="144"/>
-      <c r="BH2" s="144"/>
-      <c r="BI2" s="144"/>
-      <c r="BJ2" s="144"/>
-      <c r="BK2" s="146"/>
+      <c r="AW2" s="144" t="s">
+        <v>39</v>
+      </c>
+      <c r="AX2" s="143"/>
+      <c r="AY2" s="143"/>
+      <c r="AZ2" s="143"/>
+      <c r="BA2" s="143"/>
+      <c r="BB2" s="143"/>
+      <c r="BC2" s="143"/>
+      <c r="BD2" s="143"/>
+      <c r="BE2" s="143"/>
+      <c r="BF2" s="143"/>
+      <c r="BG2" s="143"/>
+      <c r="BH2" s="143"/>
+      <c r="BI2" s="143"/>
+      <c r="BJ2" s="143"/>
+      <c r="BK2" s="145"/>
       <c r="BL2" s="6"/>
     </row>
     <row r="3" spans="2:68" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="7"/>
       <c r="L3" s="8"/>
-      <c r="M3" s="170"/>
-      <c r="N3" s="171"/>
-      <c r="O3" s="171"/>
-      <c r="P3" s="171"/>
-      <c r="Q3" s="171"/>
-      <c r="R3" s="171"/>
-      <c r="S3" s="171"/>
-      <c r="T3" s="171"/>
-      <c r="U3" s="171"/>
-      <c r="V3" s="171"/>
-      <c r="W3" s="171"/>
-      <c r="X3" s="171"/>
-      <c r="Y3" s="171"/>
-      <c r="Z3" s="171"/>
-      <c r="AA3" s="171"/>
-      <c r="AB3" s="171"/>
-      <c r="AC3" s="171"/>
-      <c r="AD3" s="171"/>
-      <c r="AE3" s="171"/>
-      <c r="AF3" s="171"/>
-      <c r="AG3" s="171"/>
-      <c r="AH3" s="171"/>
-      <c r="AI3" s="171"/>
-      <c r="AJ3" s="171"/>
-      <c r="AK3" s="171"/>
-      <c r="AL3" s="171"/>
-      <c r="AM3" s="171"/>
-      <c r="AN3" s="171"/>
-      <c r="AO3" s="172"/>
-      <c r="AP3" s="147"/>
-      <c r="AQ3" s="148"/>
-      <c r="AR3" s="148"/>
-      <c r="AS3" s="148"/>
-      <c r="AT3" s="148"/>
-      <c r="AU3" s="148"/>
-      <c r="AV3" s="149"/>
-      <c r="AW3" s="149"/>
-      <c r="AX3" s="148"/>
-      <c r="AY3" s="148"/>
-      <c r="AZ3" s="148"/>
-      <c r="BA3" s="148"/>
-      <c r="BB3" s="148"/>
-      <c r="BC3" s="148"/>
-      <c r="BD3" s="148"/>
-      <c r="BE3" s="148"/>
-      <c r="BF3" s="148"/>
-      <c r="BG3" s="148"/>
-      <c r="BH3" s="148"/>
-      <c r="BI3" s="148"/>
-      <c r="BJ3" s="148"/>
-      <c r="BK3" s="150"/>
+      <c r="M3" s="176"/>
+      <c r="N3" s="177"/>
+      <c r="O3" s="177"/>
+      <c r="P3" s="177"/>
+      <c r="Q3" s="177"/>
+      <c r="R3" s="177"/>
+      <c r="S3" s="177"/>
+      <c r="T3" s="177"/>
+      <c r="U3" s="177"/>
+      <c r="V3" s="177"/>
+      <c r="W3" s="177"/>
+      <c r="X3" s="177"/>
+      <c r="Y3" s="177"/>
+      <c r="Z3" s="177"/>
+      <c r="AA3" s="177"/>
+      <c r="AB3" s="177"/>
+      <c r="AC3" s="177"/>
+      <c r="AD3" s="177"/>
+      <c r="AE3" s="177"/>
+      <c r="AF3" s="177"/>
+      <c r="AG3" s="177"/>
+      <c r="AH3" s="177"/>
+      <c r="AI3" s="177"/>
+      <c r="AJ3" s="177"/>
+      <c r="AK3" s="177"/>
+      <c r="AL3" s="177"/>
+      <c r="AM3" s="177"/>
+      <c r="AN3" s="177"/>
+      <c r="AO3" s="178"/>
+      <c r="AP3" s="146"/>
+      <c r="AQ3" s="147"/>
+      <c r="AR3" s="147"/>
+      <c r="AS3" s="147"/>
+      <c r="AT3" s="147"/>
+      <c r="AU3" s="147"/>
+      <c r="AV3" s="148"/>
+      <c r="AW3" s="148"/>
+      <c r="AX3" s="147"/>
+      <c r="AY3" s="147"/>
+      <c r="AZ3" s="147"/>
+      <c r="BA3" s="147"/>
+      <c r="BB3" s="147"/>
+      <c r="BC3" s="147"/>
+      <c r="BD3" s="147"/>
+      <c r="BE3" s="147"/>
+      <c r="BF3" s="147"/>
+      <c r="BG3" s="147"/>
+      <c r="BH3" s="147"/>
+      <c r="BI3" s="147"/>
+      <c r="BJ3" s="147"/>
+      <c r="BK3" s="149"/>
     </row>
     <row r="4" spans="2:68" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="7"/>
       <c r="L4" s="8"/>
-      <c r="M4" s="170"/>
-      <c r="N4" s="171"/>
-      <c r="O4" s="171"/>
-      <c r="P4" s="171"/>
-      <c r="Q4" s="171"/>
-      <c r="R4" s="171"/>
-      <c r="S4" s="171"/>
-      <c r="T4" s="171"/>
-      <c r="U4" s="171"/>
-      <c r="V4" s="171"/>
-      <c r="W4" s="171"/>
-      <c r="X4" s="171"/>
-      <c r="Y4" s="171"/>
-      <c r="Z4" s="171"/>
-      <c r="AA4" s="171"/>
-      <c r="AB4" s="171"/>
-      <c r="AC4" s="171"/>
-      <c r="AD4" s="171"/>
-      <c r="AE4" s="171"/>
-      <c r="AF4" s="171"/>
-      <c r="AG4" s="171"/>
-      <c r="AH4" s="171"/>
-      <c r="AI4" s="171"/>
-      <c r="AJ4" s="171"/>
-      <c r="AK4" s="171"/>
-      <c r="AL4" s="171"/>
-      <c r="AM4" s="171"/>
-      <c r="AN4" s="171"/>
-      <c r="AO4" s="172"/>
-      <c r="AP4" s="147"/>
-      <c r="AQ4" s="148" t="s">
+      <c r="M4" s="176"/>
+      <c r="N4" s="177"/>
+      <c r="O4" s="177"/>
+      <c r="P4" s="177"/>
+      <c r="Q4" s="177"/>
+      <c r="R4" s="177"/>
+      <c r="S4" s="177"/>
+      <c r="T4" s="177"/>
+      <c r="U4" s="177"/>
+      <c r="V4" s="177"/>
+      <c r="W4" s="177"/>
+      <c r="X4" s="177"/>
+      <c r="Y4" s="177"/>
+      <c r="Z4" s="177"/>
+      <c r="AA4" s="177"/>
+      <c r="AB4" s="177"/>
+      <c r="AC4" s="177"/>
+      <c r="AD4" s="177"/>
+      <c r="AE4" s="177"/>
+      <c r="AF4" s="177"/>
+      <c r="AG4" s="177"/>
+      <c r="AH4" s="177"/>
+      <c r="AI4" s="177"/>
+      <c r="AJ4" s="177"/>
+      <c r="AK4" s="177"/>
+      <c r="AL4" s="177"/>
+      <c r="AM4" s="177"/>
+      <c r="AN4" s="177"/>
+      <c r="AO4" s="178"/>
+      <c r="AP4" s="146"/>
+      <c r="AQ4" s="147" t="s">
         <v>3</v>
       </c>
-      <c r="AR4" s="148"/>
-      <c r="AS4" s="148"/>
-      <c r="AT4" s="148"/>
-      <c r="AU4" s="148"/>
-      <c r="AV4" s="149" t="s">
+      <c r="AR4" s="147"/>
+      <c r="AS4" s="147"/>
+      <c r="AT4" s="147"/>
+      <c r="AU4" s="147"/>
+      <c r="AV4" s="148" t="s">
         <v>2</v>
       </c>
-      <c r="AW4" s="149" t="s">
-        <v>41</v>
-      </c>
-      <c r="AX4" s="148"/>
-      <c r="AY4" s="148"/>
-      <c r="AZ4" s="148"/>
-      <c r="BA4" s="148"/>
-      <c r="BB4" s="148"/>
-      <c r="BC4" s="148"/>
-      <c r="BD4" s="148"/>
-      <c r="BE4" s="148"/>
-      <c r="BF4" s="148"/>
-      <c r="BG4" s="148"/>
-      <c r="BH4" s="148"/>
-      <c r="BI4" s="148"/>
-      <c r="BJ4" s="148"/>
-      <c r="BK4" s="150"/>
+      <c r="AW4" s="148" t="s">
+        <v>40</v>
+      </c>
+      <c r="AX4" s="147"/>
+      <c r="AY4" s="147"/>
+      <c r="AZ4" s="147"/>
+      <c r="BA4" s="147"/>
+      <c r="BB4" s="147"/>
+      <c r="BC4" s="147"/>
+      <c r="BD4" s="147"/>
+      <c r="BE4" s="147"/>
+      <c r="BF4" s="147"/>
+      <c r="BG4" s="147"/>
+      <c r="BH4" s="147"/>
+      <c r="BI4" s="147"/>
+      <c r="BJ4" s="147"/>
+      <c r="BK4" s="149"/>
       <c r="BL4" s="9"/>
     </row>
     <row r="5" spans="2:68" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1867,63 +1867,63 @@
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="173"/>
-      <c r="N5" s="174"/>
-      <c r="O5" s="174"/>
-      <c r="P5" s="174"/>
-      <c r="Q5" s="174"/>
-      <c r="R5" s="174"/>
-      <c r="S5" s="174"/>
-      <c r="T5" s="174"/>
-      <c r="U5" s="174"/>
-      <c r="V5" s="174"/>
-      <c r="W5" s="174"/>
-      <c r="X5" s="174"/>
-      <c r="Y5" s="174"/>
-      <c r="Z5" s="174"/>
-      <c r="AA5" s="174"/>
-      <c r="AB5" s="174"/>
-      <c r="AC5" s="174"/>
-      <c r="AD5" s="174"/>
-      <c r="AE5" s="174"/>
-      <c r="AF5" s="174"/>
-      <c r="AG5" s="174"/>
-      <c r="AH5" s="174"/>
-      <c r="AI5" s="174"/>
-      <c r="AJ5" s="174"/>
-      <c r="AK5" s="174"/>
-      <c r="AL5" s="174"/>
-      <c r="AM5" s="174"/>
-      <c r="AN5" s="174"/>
-      <c r="AO5" s="175"/>
-      <c r="AP5" s="151"/>
-      <c r="AQ5" s="152" t="s">
+      <c r="M5" s="179"/>
+      <c r="N5" s="180"/>
+      <c r="O5" s="180"/>
+      <c r="P5" s="180"/>
+      <c r="Q5" s="180"/>
+      <c r="R5" s="180"/>
+      <c r="S5" s="180"/>
+      <c r="T5" s="180"/>
+      <c r="U5" s="180"/>
+      <c r="V5" s="180"/>
+      <c r="W5" s="180"/>
+      <c r="X5" s="180"/>
+      <c r="Y5" s="180"/>
+      <c r="Z5" s="180"/>
+      <c r="AA5" s="180"/>
+      <c r="AB5" s="180"/>
+      <c r="AC5" s="180"/>
+      <c r="AD5" s="180"/>
+      <c r="AE5" s="180"/>
+      <c r="AF5" s="180"/>
+      <c r="AG5" s="180"/>
+      <c r="AH5" s="180"/>
+      <c r="AI5" s="180"/>
+      <c r="AJ5" s="180"/>
+      <c r="AK5" s="180"/>
+      <c r="AL5" s="180"/>
+      <c r="AM5" s="180"/>
+      <c r="AN5" s="180"/>
+      <c r="AO5" s="181"/>
+      <c r="AP5" s="150"/>
+      <c r="AQ5" s="151" t="s">
         <v>4</v>
       </c>
-      <c r="AR5" s="152"/>
-      <c r="AS5" s="152"/>
-      <c r="AT5" s="152"/>
-      <c r="AU5" s="152"/>
+      <c r="AR5" s="151"/>
+      <c r="AS5" s="151"/>
+      <c r="AT5" s="151"/>
+      <c r="AU5" s="151"/>
       <c r="AV5" s="128" t="s">
         <v>2</v>
       </c>
       <c r="AW5" s="128" t="s">
-        <v>42</v>
-      </c>
-      <c r="AX5" s="152"/>
-      <c r="AY5" s="152"/>
-      <c r="AZ5" s="152"/>
-      <c r="BA5" s="152"/>
-      <c r="BB5" s="152"/>
-      <c r="BC5" s="152"/>
-      <c r="BD5" s="152"/>
-      <c r="BE5" s="152"/>
-      <c r="BF5" s="152"/>
-      <c r="BG5" s="152"/>
-      <c r="BH5" s="152"/>
-      <c r="BI5" s="152"/>
-      <c r="BJ5" s="152"/>
-      <c r="BK5" s="153"/>
+        <v>41</v>
+      </c>
+      <c r="AX5" s="151"/>
+      <c r="AY5" s="151"/>
+      <c r="AZ5" s="151"/>
+      <c r="BA5" s="151"/>
+      <c r="BB5" s="151"/>
+      <c r="BC5" s="151"/>
+      <c r="BD5" s="151"/>
+      <c r="BE5" s="151"/>
+      <c r="BF5" s="151"/>
+      <c r="BG5" s="151"/>
+      <c r="BH5" s="151"/>
+      <c r="BI5" s="151"/>
+      <c r="BJ5" s="151"/>
+      <c r="BK5" s="152"/>
       <c r="BL5" s="13"/>
     </row>
     <row r="6" spans="2:68" ht="6.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2058,99 +2058,99 @@
       <c r="BP7" s="22"/>
     </row>
     <row r="8" spans="2:68" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="178" t="s">
+      <c r="B8" s="170" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="179"/>
-      <c r="D8" s="179"/>
-      <c r="E8" s="179"/>
-      <c r="F8" s="179"/>
-      <c r="G8" s="179"/>
-      <c r="H8" s="179"/>
-      <c r="I8" s="179"/>
-      <c r="J8" s="179"/>
-      <c r="K8" s="179"/>
-      <c r="L8" s="179"/>
-      <c r="M8" s="179"/>
-      <c r="N8" s="179"/>
-      <c r="O8" s="179"/>
-      <c r="P8" s="179"/>
-      <c r="Q8" s="179"/>
-      <c r="R8" s="179"/>
-      <c r="S8" s="179"/>
-      <c r="T8" s="179"/>
-      <c r="U8" s="179"/>
-      <c r="V8" s="179"/>
-      <c r="W8" s="180"/>
-      <c r="X8" s="178" t="s">
+      <c r="C8" s="171"/>
+      <c r="D8" s="171"/>
+      <c r="E8" s="171"/>
+      <c r="F8" s="171"/>
+      <c r="G8" s="171"/>
+      <c r="H8" s="171"/>
+      <c r="I8" s="171"/>
+      <c r="J8" s="171"/>
+      <c r="K8" s="171"/>
+      <c r="L8" s="171"/>
+      <c r="M8" s="171"/>
+      <c r="N8" s="171"/>
+      <c r="O8" s="171"/>
+      <c r="P8" s="171"/>
+      <c r="Q8" s="171"/>
+      <c r="R8" s="171"/>
+      <c r="S8" s="171"/>
+      <c r="T8" s="171"/>
+      <c r="U8" s="171"/>
+      <c r="V8" s="171"/>
+      <c r="W8" s="172"/>
+      <c r="X8" s="170" t="s">
         <v>6</v>
       </c>
-      <c r="Y8" s="179"/>
-      <c r="Z8" s="179"/>
-      <c r="AA8" s="179"/>
-      <c r="AB8" s="179"/>
-      <c r="AC8" s="179"/>
-      <c r="AD8" s="179"/>
-      <c r="AE8" s="179"/>
-      <c r="AF8" s="179"/>
-      <c r="AG8" s="179"/>
-      <c r="AH8" s="179"/>
-      <c r="AI8" s="179"/>
-      <c r="AJ8" s="179"/>
-      <c r="AK8" s="179"/>
-      <c r="AL8" s="179"/>
-      <c r="AM8" s="179"/>
-      <c r="AN8" s="179"/>
-      <c r="AO8" s="180"/>
+      <c r="Y8" s="171"/>
+      <c r="Z8" s="171"/>
+      <c r="AA8" s="171"/>
+      <c r="AB8" s="171"/>
+      <c r="AC8" s="171"/>
+      <c r="AD8" s="171"/>
+      <c r="AE8" s="171"/>
+      <c r="AF8" s="171"/>
+      <c r="AG8" s="171"/>
+      <c r="AH8" s="171"/>
+      <c r="AI8" s="171"/>
+      <c r="AJ8" s="171"/>
+      <c r="AK8" s="171"/>
+      <c r="AL8" s="171"/>
+      <c r="AM8" s="171"/>
+      <c r="AN8" s="171"/>
+      <c r="AO8" s="172"/>
       <c r="AP8" s="24"/>
-      <c r="AQ8" s="178" t="s">
+      <c r="AQ8" s="170" t="s">
         <v>7</v>
       </c>
-      <c r="AR8" s="179"/>
-      <c r="AS8" s="179"/>
-      <c r="AT8" s="179"/>
-      <c r="AU8" s="179"/>
-      <c r="AV8" s="179"/>
-      <c r="AW8" s="179"/>
-      <c r="AX8" s="179"/>
-      <c r="AY8" s="179"/>
-      <c r="AZ8" s="179"/>
-      <c r="BA8" s="179"/>
-      <c r="BB8" s="179"/>
-      <c r="BC8" s="179"/>
-      <c r="BD8" s="179"/>
-      <c r="BE8" s="179"/>
-      <c r="BF8" s="179"/>
-      <c r="BG8" s="179"/>
-      <c r="BH8" s="179"/>
-      <c r="BI8" s="179"/>
-      <c r="BJ8" s="179"/>
-      <c r="BK8" s="180"/>
+      <c r="AR8" s="171"/>
+      <c r="AS8" s="171"/>
+      <c r="AT8" s="171"/>
+      <c r="AU8" s="171"/>
+      <c r="AV8" s="171"/>
+      <c r="AW8" s="171"/>
+      <c r="AX8" s="171"/>
+      <c r="AY8" s="171"/>
+      <c r="AZ8" s="171"/>
+      <c r="BA8" s="171"/>
+      <c r="BB8" s="171"/>
+      <c r="BC8" s="171"/>
+      <c r="BD8" s="171"/>
+      <c r="BE8" s="171"/>
+      <c r="BF8" s="171"/>
+      <c r="BG8" s="171"/>
+      <c r="BH8" s="171"/>
+      <c r="BI8" s="171"/>
+      <c r="BJ8" s="171"/>
+      <c r="BK8" s="172"/>
       <c r="BL8" s="1"/>
       <c r="BN8" s="22"/>
     </row>
     <row r="9" spans="2:68" ht="16.7" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B9" s="7"/>
-      <c r="X9" s="185" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y9" s="186"/>
-      <c r="Z9" s="186"/>
-      <c r="AA9" s="186"/>
-      <c r="AB9" s="186"/>
-      <c r="AC9" s="186"/>
-      <c r="AD9" s="186"/>
-      <c r="AE9" s="186"/>
-      <c r="AF9" s="186"/>
-      <c r="AG9" s="186"/>
-      <c r="AH9" s="186"/>
-      <c r="AI9" s="186"/>
-      <c r="AJ9" s="186"/>
-      <c r="AK9" s="186"/>
-      <c r="AL9" s="186"/>
-      <c r="AM9" s="186"/>
-      <c r="AN9" s="186"/>
-      <c r="AO9" s="187"/>
+      <c r="X9" s="188" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y9" s="189"/>
+      <c r="Z9" s="189"/>
+      <c r="AA9" s="189"/>
+      <c r="AB9" s="189"/>
+      <c r="AC9" s="189"/>
+      <c r="AD9" s="189"/>
+      <c r="AE9" s="189"/>
+      <c r="AF9" s="189"/>
+      <c r="AG9" s="189"/>
+      <c r="AH9" s="189"/>
+      <c r="AI9" s="189"/>
+      <c r="AJ9" s="189"/>
+      <c r="AK9" s="189"/>
+      <c r="AL9" s="189"/>
+      <c r="AM9" s="189"/>
+      <c r="AN9" s="189"/>
+      <c r="AO9" s="190"/>
       <c r="AP9" s="7"/>
       <c r="AQ9" s="25" t="s">
         <v>8</v>
@@ -2161,24 +2161,24 @@
     </row>
     <row r="10" spans="2:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="7"/>
-      <c r="X10" s="188"/>
-      <c r="Y10" s="189"/>
-      <c r="Z10" s="189"/>
-      <c r="AA10" s="189"/>
-      <c r="AB10" s="189"/>
-      <c r="AC10" s="189"/>
-      <c r="AD10" s="189"/>
-      <c r="AE10" s="189"/>
-      <c r="AF10" s="189"/>
-      <c r="AG10" s="189"/>
-      <c r="AH10" s="189"/>
-      <c r="AI10" s="189"/>
-      <c r="AJ10" s="189"/>
-      <c r="AK10" s="189"/>
-      <c r="AL10" s="189"/>
-      <c r="AM10" s="189"/>
-      <c r="AN10" s="189"/>
-      <c r="AO10" s="190"/>
+      <c r="X10" s="191"/>
+      <c r="Y10" s="192"/>
+      <c r="Z10" s="192"/>
+      <c r="AA10" s="192"/>
+      <c r="AB10" s="192"/>
+      <c r="AC10" s="192"/>
+      <c r="AD10" s="192"/>
+      <c r="AE10" s="192"/>
+      <c r="AF10" s="192"/>
+      <c r="AG10" s="192"/>
+      <c r="AH10" s="192"/>
+      <c r="AI10" s="192"/>
+      <c r="AJ10" s="192"/>
+      <c r="AK10" s="192"/>
+      <c r="AL10" s="192"/>
+      <c r="AM10" s="192"/>
+      <c r="AN10" s="192"/>
+      <c r="AO10" s="193"/>
       <c r="AP10" s="26"/>
       <c r="AQ10" s="33"/>
       <c r="AR10" s="49"/>
@@ -2202,24 +2202,24 @@
     <row r="11" spans="2:68" ht="16.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B11" s="7"/>
       <c r="W11" s="8"/>
-      <c r="X11" s="191"/>
-      <c r="Y11" s="192"/>
-      <c r="Z11" s="192"/>
-      <c r="AA11" s="192"/>
-      <c r="AB11" s="192"/>
-      <c r="AC11" s="192"/>
-      <c r="AD11" s="192"/>
-      <c r="AE11" s="192"/>
-      <c r="AF11" s="192"/>
-      <c r="AG11" s="192"/>
-      <c r="AH11" s="192"/>
-      <c r="AI11" s="192"/>
-      <c r="AJ11" s="192"/>
-      <c r="AK11" s="192"/>
-      <c r="AL11" s="192"/>
-      <c r="AM11" s="192"/>
-      <c r="AN11" s="192"/>
-      <c r="AO11" s="193"/>
+      <c r="X11" s="194"/>
+      <c r="Y11" s="195"/>
+      <c r="Z11" s="195"/>
+      <c r="AA11" s="195"/>
+      <c r="AB11" s="195"/>
+      <c r="AC11" s="195"/>
+      <c r="AD11" s="195"/>
+      <c r="AE11" s="195"/>
+      <c r="AF11" s="195"/>
+      <c r="AG11" s="195"/>
+      <c r="AH11" s="195"/>
+      <c r="AI11" s="195"/>
+      <c r="AJ11" s="195"/>
+      <c r="AK11" s="195"/>
+      <c r="AL11" s="195"/>
+      <c r="AM11" s="195"/>
+      <c r="AN11" s="195"/>
+      <c r="AO11" s="196"/>
       <c r="AP11" s="26"/>
       <c r="AQ11" s="57"/>
       <c r="AR11" s="56"/>
@@ -2244,26 +2244,26 @@
     <row r="12" spans="2:68" ht="16.7" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="7"/>
       <c r="W12" s="8"/>
-      <c r="X12" s="178" t="s">
+      <c r="X12" s="170" t="s">
         <v>9</v>
       </c>
-      <c r="Y12" s="179"/>
-      <c r="Z12" s="179"/>
-      <c r="AA12" s="179"/>
-      <c r="AB12" s="179"/>
-      <c r="AC12" s="179"/>
-      <c r="AD12" s="179"/>
-      <c r="AE12" s="179"/>
-      <c r="AF12" s="179"/>
-      <c r="AG12" s="179"/>
-      <c r="AH12" s="179"/>
-      <c r="AI12" s="179"/>
-      <c r="AJ12" s="179"/>
-      <c r="AK12" s="179"/>
-      <c r="AL12" s="179"/>
-      <c r="AM12" s="179"/>
-      <c r="AN12" s="179"/>
-      <c r="AO12" s="180"/>
+      <c r="Y12" s="171"/>
+      <c r="Z12" s="171"/>
+      <c r="AA12" s="171"/>
+      <c r="AB12" s="171"/>
+      <c r="AC12" s="171"/>
+      <c r="AD12" s="171"/>
+      <c r="AE12" s="171"/>
+      <c r="AF12" s="171"/>
+      <c r="AG12" s="171"/>
+      <c r="AH12" s="171"/>
+      <c r="AI12" s="171"/>
+      <c r="AJ12" s="171"/>
+      <c r="AK12" s="171"/>
+      <c r="AL12" s="171"/>
+      <c r="AM12" s="171"/>
+      <c r="AN12" s="171"/>
+      <c r="AO12" s="172"/>
       <c r="AP12" s="26"/>
       <c r="AQ12" s="129" t="s">
         <v>10</v>
@@ -2405,7 +2405,7 @@
       <c r="AN16" s="22"/>
       <c r="AO16" s="22"/>
       <c r="AP16" s="26"/>
-      <c r="AQ16" s="141"/>
+      <c r="AQ16" s="140"/>
       <c r="AR16" s="57"/>
       <c r="AS16" s="22"/>
       <c r="AT16" s="49"/>
@@ -2447,7 +2447,7 @@
       <c r="Y17" s="55"/>
       <c r="Z17" s="56"/>
       <c r="AP17" s="37"/>
-      <c r="AQ17" s="142"/>
+      <c r="AQ17" s="141"/>
       <c r="AR17" s="56"/>
       <c r="AT17" s="56"/>
       <c r="AU17" s="56"/>
@@ -2487,7 +2487,7 @@
       <c r="Y18" s="55"/>
       <c r="Z18" s="56"/>
       <c r="AP18" s="37"/>
-      <c r="AQ18" s="142"/>
+      <c r="AQ18" s="141"/>
       <c r="AR18" s="56"/>
       <c r="AT18" s="56"/>
       <c r="AU18" s="56"/>
@@ -2526,7 +2526,7 @@
       <c r="X19" s="35"/>
       <c r="Y19" s="31"/>
       <c r="AP19" s="37"/>
-      <c r="AQ19" s="142"/>
+      <c r="AQ19" s="141"/>
       <c r="AR19" s="56"/>
       <c r="AT19" s="56"/>
       <c r="AU19" s="56"/>
@@ -2565,7 +2565,7 @@
       <c r="X20" s="35"/>
       <c r="Y20" s="31"/>
       <c r="AP20" s="37"/>
-      <c r="AQ20" s="142"/>
+      <c r="AQ20" s="141"/>
       <c r="AR20" s="56"/>
       <c r="AT20" s="56"/>
       <c r="AU20" s="56"/>
@@ -2603,7 +2603,7 @@
       <c r="W21" s="8"/>
       <c r="X21" s="35"/>
       <c r="AP21" s="37"/>
-      <c r="AQ21" s="142"/>
+      <c r="AQ21" s="141"/>
       <c r="AR21" s="56"/>
       <c r="AT21" s="56"/>
       <c r="AU21" s="56"/>
@@ -2634,14 +2634,14 @@
       <c r="K22" s="11"/>
       <c r="L22" s="11"/>
       <c r="M22" s="128" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N22" s="128"/>
       <c r="O22" s="128"/>
       <c r="P22" s="128"/>
       <c r="Q22" s="128"/>
       <c r="R22" s="128" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="S22" s="128"/>
       <c r="T22" s="11"/>
@@ -2691,70 +2691,70 @@
       <c r="BN22" s="22"/>
     </row>
     <row r="23" spans="2:68" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="178" t="s">
+      <c r="B23" s="170" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="179"/>
-      <c r="D23" s="179"/>
-      <c r="E23" s="179"/>
-      <c r="F23" s="179"/>
-      <c r="G23" s="179"/>
-      <c r="H23" s="179"/>
-      <c r="I23" s="179"/>
-      <c r="J23" s="179"/>
-      <c r="K23" s="179"/>
-      <c r="L23" s="179"/>
-      <c r="M23" s="179"/>
-      <c r="N23" s="179"/>
-      <c r="O23" s="179"/>
-      <c r="P23" s="179"/>
-      <c r="Q23" s="179"/>
-      <c r="R23" s="179"/>
-      <c r="S23" s="179"/>
-      <c r="T23" s="179"/>
-      <c r="U23" s="179"/>
-      <c r="V23" s="179"/>
-      <c r="W23" s="179"/>
-      <c r="X23" s="179"/>
-      <c r="Y23" s="179"/>
-      <c r="Z23" s="179"/>
-      <c r="AA23" s="179"/>
-      <c r="AB23" s="179"/>
-      <c r="AC23" s="179"/>
-      <c r="AD23" s="179"/>
-      <c r="AE23" s="179"/>
-      <c r="AF23" s="179"/>
-      <c r="AG23" s="179"/>
-      <c r="AH23" s="179"/>
-      <c r="AI23" s="179"/>
-      <c r="AJ23" s="179"/>
-      <c r="AK23" s="179"/>
-      <c r="AL23" s="179"/>
-      <c r="AM23" s="179"/>
-      <c r="AN23" s="179"/>
-      <c r="AO23" s="179"/>
-      <c r="AP23" s="179"/>
-      <c r="AQ23" s="179"/>
-      <c r="AR23" s="179"/>
-      <c r="AS23" s="179"/>
-      <c r="AT23" s="179"/>
-      <c r="AU23" s="179"/>
-      <c r="AV23" s="179"/>
-      <c r="AW23" s="179"/>
-      <c r="AX23" s="179"/>
-      <c r="AY23" s="179"/>
-      <c r="AZ23" s="179"/>
-      <c r="BA23" s="179"/>
-      <c r="BB23" s="179"/>
-      <c r="BC23" s="179"/>
-      <c r="BD23" s="179"/>
-      <c r="BE23" s="179"/>
-      <c r="BF23" s="179"/>
-      <c r="BG23" s="179"/>
-      <c r="BH23" s="179"/>
-      <c r="BI23" s="179"/>
-      <c r="BJ23" s="179"/>
-      <c r="BK23" s="180"/>
+      <c r="C23" s="171"/>
+      <c r="D23" s="171"/>
+      <c r="E23" s="171"/>
+      <c r="F23" s="171"/>
+      <c r="G23" s="171"/>
+      <c r="H23" s="171"/>
+      <c r="I23" s="171"/>
+      <c r="J23" s="171"/>
+      <c r="K23" s="171"/>
+      <c r="L23" s="171"/>
+      <c r="M23" s="171"/>
+      <c r="N23" s="171"/>
+      <c r="O23" s="171"/>
+      <c r="P23" s="171"/>
+      <c r="Q23" s="171"/>
+      <c r="R23" s="171"/>
+      <c r="S23" s="171"/>
+      <c r="T23" s="171"/>
+      <c r="U23" s="171"/>
+      <c r="V23" s="171"/>
+      <c r="W23" s="171"/>
+      <c r="X23" s="171"/>
+      <c r="Y23" s="171"/>
+      <c r="Z23" s="171"/>
+      <c r="AA23" s="171"/>
+      <c r="AB23" s="171"/>
+      <c r="AC23" s="171"/>
+      <c r="AD23" s="171"/>
+      <c r="AE23" s="171"/>
+      <c r="AF23" s="171"/>
+      <c r="AG23" s="171"/>
+      <c r="AH23" s="171"/>
+      <c r="AI23" s="171"/>
+      <c r="AJ23" s="171"/>
+      <c r="AK23" s="171"/>
+      <c r="AL23" s="171"/>
+      <c r="AM23" s="171"/>
+      <c r="AN23" s="171"/>
+      <c r="AO23" s="171"/>
+      <c r="AP23" s="171"/>
+      <c r="AQ23" s="171"/>
+      <c r="AR23" s="171"/>
+      <c r="AS23" s="171"/>
+      <c r="AT23" s="171"/>
+      <c r="AU23" s="171"/>
+      <c r="AV23" s="171"/>
+      <c r="AW23" s="171"/>
+      <c r="AX23" s="171"/>
+      <c r="AY23" s="171"/>
+      <c r="AZ23" s="171"/>
+      <c r="BA23" s="171"/>
+      <c r="BB23" s="171"/>
+      <c r="BC23" s="171"/>
+      <c r="BD23" s="171"/>
+      <c r="BE23" s="171"/>
+      <c r="BF23" s="171"/>
+      <c r="BG23" s="171"/>
+      <c r="BH23" s="171"/>
+      <c r="BI23" s="171"/>
+      <c r="BJ23" s="171"/>
+      <c r="BK23" s="172"/>
     </row>
     <row r="24" spans="2:68" ht="16.7" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B24" s="40" t="s">
@@ -3050,8 +3050,8 @@
       <c r="BP29" s="22"/>
     </row>
     <row r="30" spans="2:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="163" t="s">
-        <v>47</v>
+      <c r="B30" s="162" t="s">
+        <v>46</v>
       </c>
       <c r="C30" s="33"/>
       <c r="D30" s="22"/>
@@ -3077,7 +3077,7 @@
       <c r="BP30" s="36"/>
     </row>
     <row r="31" spans="2:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="162"/>
+      <c r="B31" s="161"/>
       <c r="C31" s="56"/>
       <c r="AO31" s="48"/>
       <c r="AP31" s="7"/>
@@ -3102,7 +3102,7 @@
       <c r="BP31" s="36"/>
     </row>
     <row r="32" spans="2:68" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="160"/>
+      <c r="B32" s="159"/>
       <c r="C32" s="56"/>
       <c r="AO32" s="48"/>
       <c r="AP32" s="7"/>
@@ -3127,7 +3127,7 @@
       <c r="BP32" s="36"/>
     </row>
     <row r="33" spans="1:87" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="162"/>
+      <c r="B33" s="161"/>
       <c r="C33" s="56"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -3154,7 +3154,7 @@
       <c r="BN33" s="57"/>
     </row>
     <row r="34" spans="1:87" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="160"/>
+      <c r="B34" s="159"/>
       <c r="C34" s="56"/>
       <c r="D34" s="58"/>
       <c r="E34" s="58"/>
@@ -3194,7 +3194,7 @@
       <c r="BO34" s="22"/>
     </row>
     <row r="35" spans="1:87" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="162"/>
+      <c r="B35" s="161"/>
       <c r="C35" s="60"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
@@ -3222,7 +3222,7 @@
       <c r="BN35" s="57"/>
     </row>
     <row r="36" spans="1:87" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="160"/>
+      <c r="B36" s="159"/>
       <c r="C36" s="61"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -3256,7 +3256,7 @@
       <c r="BP36" s="22"/>
     </row>
     <row r="37" spans="1:87" ht="16.7" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="162"/>
+      <c r="B37" s="161"/>
       <c r="C37" s="60"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -3289,8 +3289,8 @@
       <c r="BK37" s="8"/>
     </row>
     <row r="38" spans="1:87" ht="16.7" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="196"/>
-      <c r="C38" s="197"/>
+      <c r="B38" s="167"/>
+      <c r="C38" s="168"/>
       <c r="D38" s="28"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -3309,80 +3309,80 @@
       <c r="T38" s="1"/>
       <c r="AO38" s="8"/>
       <c r="AP38" s="37"/>
-      <c r="AQ38" s="196"/>
+      <c r="AQ38" s="167"/>
       <c r="AR38" s="33"/>
       <c r="BK38" s="8"/>
     </row>
     <row r="39" spans="1:87" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="195"/>
+      <c r="B39" s="166"/>
       <c r="C39" s="64"/>
       <c r="D39" s="31"/>
       <c r="E39" s="58"/>
     </row>
     <row r="40" spans="1:87" s="1" customFormat="1" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2"/>
-      <c r="B40" s="181"/>
-      <c r="C40" s="181"/>
-      <c r="D40" s="181"/>
-      <c r="E40" s="181"/>
-      <c r="F40" s="181"/>
-      <c r="G40" s="181"/>
-      <c r="H40" s="181"/>
-      <c r="I40" s="181"/>
-      <c r="J40" s="181"/>
-      <c r="K40" s="181"/>
-      <c r="L40" s="181"/>
-      <c r="M40" s="181"/>
-      <c r="N40" s="181"/>
-      <c r="O40" s="181"/>
-      <c r="P40" s="181"/>
-      <c r="Q40" s="181"/>
-      <c r="R40" s="181"/>
-      <c r="S40" s="181"/>
-      <c r="T40" s="181"/>
-      <c r="U40" s="181"/>
-      <c r="V40" s="181"/>
-      <c r="W40" s="181"/>
-      <c r="X40" s="181"/>
-      <c r="Y40" s="181"/>
-      <c r="Z40" s="181"/>
-      <c r="AA40" s="181"/>
-      <c r="AB40" s="181"/>
-      <c r="AC40" s="181"/>
-      <c r="AD40" s="181"/>
-      <c r="AE40" s="181"/>
-      <c r="AF40" s="181"/>
-      <c r="AG40" s="181"/>
-      <c r="AH40" s="181"/>
-      <c r="AI40" s="181"/>
-      <c r="AJ40" s="181"/>
-      <c r="AK40" s="181"/>
-      <c r="AL40" s="181"/>
-      <c r="AM40" s="181"/>
-      <c r="AN40" s="181"/>
-      <c r="AO40" s="181"/>
-      <c r="AP40" s="181"/>
-      <c r="AQ40" s="181"/>
-      <c r="AR40" s="181"/>
-      <c r="AS40" s="181"/>
-      <c r="AT40" s="181"/>
-      <c r="AU40" s="181"/>
-      <c r="AV40" s="181"/>
-      <c r="AW40" s="181"/>
-      <c r="AX40" s="181"/>
-      <c r="AY40" s="181"/>
-      <c r="AZ40" s="181"/>
-      <c r="BA40" s="181"/>
-      <c r="BB40" s="181"/>
-      <c r="BC40" s="181"/>
-      <c r="BD40" s="181"/>
-      <c r="BE40" s="181"/>
-      <c r="BF40" s="181"/>
-      <c r="BG40" s="181"/>
-      <c r="BH40" s="181"/>
-      <c r="BI40" s="181"/>
-      <c r="BJ40" s="181"/>
-      <c r="BK40" s="181"/>
+      <c r="B40" s="184"/>
+      <c r="C40" s="184"/>
+      <c r="D40" s="184"/>
+      <c r="E40" s="184"/>
+      <c r="F40" s="184"/>
+      <c r="G40" s="184"/>
+      <c r="H40" s="184"/>
+      <c r="I40" s="184"/>
+      <c r="J40" s="184"/>
+      <c r="K40" s="184"/>
+      <c r="L40" s="184"/>
+      <c r="M40" s="184"/>
+      <c r="N40" s="184"/>
+      <c r="O40" s="184"/>
+      <c r="P40" s="184"/>
+      <c r="Q40" s="184"/>
+      <c r="R40" s="184"/>
+      <c r="S40" s="184"/>
+      <c r="T40" s="184"/>
+      <c r="U40" s="184"/>
+      <c r="V40" s="184"/>
+      <c r="W40" s="184"/>
+      <c r="X40" s="184"/>
+      <c r="Y40" s="184"/>
+      <c r="Z40" s="184"/>
+      <c r="AA40" s="184"/>
+      <c r="AB40" s="184"/>
+      <c r="AC40" s="184"/>
+      <c r="AD40" s="184"/>
+      <c r="AE40" s="184"/>
+      <c r="AF40" s="184"/>
+      <c r="AG40" s="184"/>
+      <c r="AH40" s="184"/>
+      <c r="AI40" s="184"/>
+      <c r="AJ40" s="184"/>
+      <c r="AK40" s="184"/>
+      <c r="AL40" s="184"/>
+      <c r="AM40" s="184"/>
+      <c r="AN40" s="184"/>
+      <c r="AO40" s="184"/>
+      <c r="AP40" s="184"/>
+      <c r="AQ40" s="184"/>
+      <c r="AR40" s="184"/>
+      <c r="AS40" s="184"/>
+      <c r="AT40" s="184"/>
+      <c r="AU40" s="184"/>
+      <c r="AV40" s="184"/>
+      <c r="AW40" s="184"/>
+      <c r="AX40" s="184"/>
+      <c r="AY40" s="184"/>
+      <c r="AZ40" s="184"/>
+      <c r="BA40" s="184"/>
+      <c r="BB40" s="184"/>
+      <c r="BC40" s="184"/>
+      <c r="BD40" s="184"/>
+      <c r="BE40" s="184"/>
+      <c r="BF40" s="184"/>
+      <c r="BG40" s="184"/>
+      <c r="BH40" s="184"/>
+      <c r="BI40" s="184"/>
+      <c r="BJ40" s="184"/>
+      <c r="BK40" s="184"/>
       <c r="BL40" s="2"/>
     </row>
     <row r="41" spans="1:87" ht="21.95" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
@@ -3397,188 +3397,188 @@
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
       <c r="L41" s="5"/>
-      <c r="M41" s="167" t="s">
+      <c r="M41" s="173" t="s">
         <v>0</v>
       </c>
-      <c r="N41" s="168"/>
-      <c r="O41" s="168"/>
-      <c r="P41" s="168"/>
-      <c r="Q41" s="168"/>
-      <c r="R41" s="168"/>
-      <c r="S41" s="168"/>
-      <c r="T41" s="168"/>
-      <c r="U41" s="168"/>
-      <c r="V41" s="168"/>
-      <c r="W41" s="168"/>
-      <c r="X41" s="168"/>
-      <c r="Y41" s="168"/>
-      <c r="Z41" s="168"/>
-      <c r="AA41" s="168"/>
-      <c r="AB41" s="168"/>
-      <c r="AC41" s="168"/>
-      <c r="AD41" s="168"/>
-      <c r="AE41" s="168"/>
-      <c r="AF41" s="168"/>
-      <c r="AG41" s="168"/>
-      <c r="AH41" s="168"/>
-      <c r="AI41" s="168"/>
-      <c r="AJ41" s="168"/>
-      <c r="AK41" s="168"/>
-      <c r="AL41" s="168"/>
-      <c r="AM41" s="168"/>
-      <c r="AN41" s="168"/>
-      <c r="AO41" s="169"/>
-      <c r="AP41" s="154"/>
-      <c r="AQ41" s="144" t="str">
+      <c r="N41" s="174"/>
+      <c r="O41" s="174"/>
+      <c r="P41" s="174"/>
+      <c r="Q41" s="174"/>
+      <c r="R41" s="174"/>
+      <c r="S41" s="174"/>
+      <c r="T41" s="174"/>
+      <c r="U41" s="174"/>
+      <c r="V41" s="174"/>
+      <c r="W41" s="174"/>
+      <c r="X41" s="174"/>
+      <c r="Y41" s="174"/>
+      <c r="Z41" s="174"/>
+      <c r="AA41" s="174"/>
+      <c r="AB41" s="174"/>
+      <c r="AC41" s="174"/>
+      <c r="AD41" s="174"/>
+      <c r="AE41" s="174"/>
+      <c r="AF41" s="174"/>
+      <c r="AG41" s="174"/>
+      <c r="AH41" s="174"/>
+      <c r="AI41" s="174"/>
+      <c r="AJ41" s="174"/>
+      <c r="AK41" s="174"/>
+      <c r="AL41" s="174"/>
+      <c r="AM41" s="174"/>
+      <c r="AN41" s="174"/>
+      <c r="AO41" s="175"/>
+      <c r="AP41" s="153"/>
+      <c r="AQ41" s="143" t="str">
         <f>$AQ$2</f>
         <v>Divisi</v>
       </c>
-      <c r="AR41" s="144"/>
-      <c r="AS41" s="144"/>
-      <c r="AT41" s="144"/>
-      <c r="AU41" s="144"/>
-      <c r="AV41" s="145" t="str">
+      <c r="AR41" s="143"/>
+      <c r="AS41" s="143"/>
+      <c r="AT41" s="143"/>
+      <c r="AU41" s="143"/>
+      <c r="AV41" s="144" t="str">
         <f>$AV$2</f>
         <v xml:space="preserve">:  </v>
       </c>
-      <c r="AW41" s="145" t="str">
+      <c r="AW41" s="144" t="str">
         <f>$AW$2</f>
         <v>DivisionName</v>
       </c>
-      <c r="AX41" s="144"/>
-      <c r="AY41" s="144"/>
-      <c r="AZ41" s="144"/>
-      <c r="BA41" s="144"/>
-      <c r="BB41" s="144"/>
-      <c r="BC41" s="144"/>
-      <c r="BD41" s="144"/>
-      <c r="BE41" s="144"/>
-      <c r="BF41" s="144"/>
-      <c r="BG41" s="144"/>
-      <c r="BH41" s="144"/>
-      <c r="BI41" s="144"/>
-      <c r="BJ41" s="144"/>
-      <c r="BK41" s="146"/>
+      <c r="AX41" s="143"/>
+      <c r="AY41" s="143"/>
+      <c r="AZ41" s="143"/>
+      <c r="BA41" s="143"/>
+      <c r="BB41" s="143"/>
+      <c r="BC41" s="143"/>
+      <c r="BD41" s="143"/>
+      <c r="BE41" s="143"/>
+      <c r="BF41" s="143"/>
+      <c r="BG41" s="143"/>
+      <c r="BH41" s="143"/>
+      <c r="BI41" s="143"/>
+      <c r="BJ41" s="143"/>
+      <c r="BK41" s="145"/>
       <c r="BL41" s="6"/>
     </row>
     <row r="42" spans="1:87" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="7"/>
       <c r="L42" s="8"/>
-      <c r="M42" s="170"/>
-      <c r="N42" s="171"/>
-      <c r="O42" s="171"/>
-      <c r="P42" s="171"/>
-      <c r="Q42" s="171"/>
-      <c r="R42" s="171"/>
-      <c r="S42" s="171"/>
-      <c r="T42" s="171"/>
-      <c r="U42" s="171"/>
-      <c r="V42" s="171"/>
-      <c r="W42" s="171"/>
-      <c r="X42" s="171"/>
-      <c r="Y42" s="171"/>
-      <c r="Z42" s="171"/>
-      <c r="AA42" s="171"/>
-      <c r="AB42" s="171"/>
-      <c r="AC42" s="171"/>
-      <c r="AD42" s="171"/>
-      <c r="AE42" s="171"/>
-      <c r="AF42" s="171"/>
-      <c r="AG42" s="171"/>
-      <c r="AH42" s="171"/>
-      <c r="AI42" s="171"/>
-      <c r="AJ42" s="171"/>
-      <c r="AK42" s="171"/>
-      <c r="AL42" s="171"/>
-      <c r="AM42" s="171"/>
-      <c r="AN42" s="171"/>
-      <c r="AO42" s="172"/>
-      <c r="AP42" s="155"/>
+      <c r="M42" s="176"/>
+      <c r="N42" s="177"/>
+      <c r="O42" s="177"/>
+      <c r="P42" s="177"/>
+      <c r="Q42" s="177"/>
+      <c r="R42" s="177"/>
+      <c r="S42" s="177"/>
+      <c r="T42" s="177"/>
+      <c r="U42" s="177"/>
+      <c r="V42" s="177"/>
+      <c r="W42" s="177"/>
+      <c r="X42" s="177"/>
+      <c r="Y42" s="177"/>
+      <c r="Z42" s="177"/>
+      <c r="AA42" s="177"/>
+      <c r="AB42" s="177"/>
+      <c r="AC42" s="177"/>
+      <c r="AD42" s="177"/>
+      <c r="AE42" s="177"/>
+      <c r="AF42" s="177"/>
+      <c r="AG42" s="177"/>
+      <c r="AH42" s="177"/>
+      <c r="AI42" s="177"/>
+      <c r="AJ42" s="177"/>
+      <c r="AK42" s="177"/>
+      <c r="AL42" s="177"/>
+      <c r="AM42" s="177"/>
+      <c r="AN42" s="177"/>
+      <c r="AO42" s="178"/>
+      <c r="AP42" s="154"/>
       <c r="AQ42" s="129" t="str">
         <f>$AQ$4</f>
         <v>Departemen</v>
       </c>
-      <c r="AR42" s="148"/>
-      <c r="AS42" s="148"/>
-      <c r="AT42" s="148"/>
-      <c r="AU42" s="148"/>
-      <c r="AV42" s="149" t="str">
+      <c r="AR42" s="147"/>
+      <c r="AS42" s="147"/>
+      <c r="AT42" s="147"/>
+      <c r="AU42" s="147"/>
+      <c r="AV42" s="148" t="str">
         <f>$AV$4</f>
         <v xml:space="preserve">:  </v>
       </c>
-      <c r="AW42" s="149" t="str">
+      <c r="AW42" s="148" t="str">
         <f>$AW$4</f>
         <v>DepartmentName</v>
       </c>
-      <c r="AX42" s="148"/>
-      <c r="AY42" s="148"/>
-      <c r="AZ42" s="148"/>
-      <c r="BA42" s="148"/>
-      <c r="BB42" s="148"/>
-      <c r="BC42" s="148"/>
-      <c r="BD42" s="148"/>
-      <c r="BE42" s="148"/>
-      <c r="BF42" s="148"/>
-      <c r="BG42" s="148"/>
-      <c r="BH42" s="148"/>
-      <c r="BI42" s="148"/>
-      <c r="BJ42" s="148"/>
-      <c r="BK42" s="150"/>
+      <c r="AX42" s="147"/>
+      <c r="AY42" s="147"/>
+      <c r="AZ42" s="147"/>
+      <c r="BA42" s="147"/>
+      <c r="BB42" s="147"/>
+      <c r="BC42" s="147"/>
+      <c r="BD42" s="147"/>
+      <c r="BE42" s="147"/>
+      <c r="BF42" s="147"/>
+      <c r="BG42" s="147"/>
+      <c r="BH42" s="147"/>
+      <c r="BI42" s="147"/>
+      <c r="BJ42" s="147"/>
+      <c r="BK42" s="149"/>
     </row>
     <row r="43" spans="1:87" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="7"/>
       <c r="L43" s="8"/>
-      <c r="M43" s="170"/>
-      <c r="N43" s="171"/>
-      <c r="O43" s="171"/>
-      <c r="P43" s="171"/>
-      <c r="Q43" s="171"/>
-      <c r="R43" s="171"/>
-      <c r="S43" s="171"/>
-      <c r="T43" s="171"/>
-      <c r="U43" s="171"/>
-      <c r="V43" s="171"/>
-      <c r="W43" s="171"/>
-      <c r="X43" s="171"/>
-      <c r="Y43" s="171"/>
-      <c r="Z43" s="171"/>
-      <c r="AA43" s="171"/>
-      <c r="AB43" s="171"/>
-      <c r="AC43" s="171"/>
-      <c r="AD43" s="171"/>
-      <c r="AE43" s="171"/>
-      <c r="AF43" s="171"/>
-      <c r="AG43" s="171"/>
-      <c r="AH43" s="171"/>
-      <c r="AI43" s="171"/>
-      <c r="AJ43" s="171"/>
-      <c r="AK43" s="171"/>
-      <c r="AL43" s="171"/>
-      <c r="AM43" s="171"/>
-      <c r="AN43" s="171"/>
-      <c r="AO43" s="172"/>
-      <c r="AP43" s="156"/>
-      <c r="AQ43" s="148"/>
-      <c r="AR43" s="148"/>
-      <c r="AS43" s="148"/>
-      <c r="AT43" s="148"/>
-      <c r="AU43" s="148"/>
-      <c r="AV43" s="149"/>
-      <c r="AW43" s="149"/>
-      <c r="AX43" s="148"/>
-      <c r="AY43" s="148"/>
-      <c r="AZ43" s="148"/>
-      <c r="BA43" s="148"/>
-      <c r="BB43" s="148"/>
-      <c r="BC43" s="148"/>
-      <c r="BD43" s="148"/>
-      <c r="BE43" s="148"/>
-      <c r="BF43" s="148"/>
-      <c r="BG43" s="148"/>
-      <c r="BH43" s="148"/>
-      <c r="BI43" s="148"/>
-      <c r="BJ43" s="148"/>
-      <c r="BK43" s="150"/>
+      <c r="M43" s="176"/>
+      <c r="N43" s="177"/>
+      <c r="O43" s="177"/>
+      <c r="P43" s="177"/>
+      <c r="Q43" s="177"/>
+      <c r="R43" s="177"/>
+      <c r="S43" s="177"/>
+      <c r="T43" s="177"/>
+      <c r="U43" s="177"/>
+      <c r="V43" s="177"/>
+      <c r="W43" s="177"/>
+      <c r="X43" s="177"/>
+      <c r="Y43" s="177"/>
+      <c r="Z43" s="177"/>
+      <c r="AA43" s="177"/>
+      <c r="AB43" s="177"/>
+      <c r="AC43" s="177"/>
+      <c r="AD43" s="177"/>
+      <c r="AE43" s="177"/>
+      <c r="AF43" s="177"/>
+      <c r="AG43" s="177"/>
+      <c r="AH43" s="177"/>
+      <c r="AI43" s="177"/>
+      <c r="AJ43" s="177"/>
+      <c r="AK43" s="177"/>
+      <c r="AL43" s="177"/>
+      <c r="AM43" s="177"/>
+      <c r="AN43" s="177"/>
+      <c r="AO43" s="178"/>
+      <c r="AP43" s="155"/>
+      <c r="AQ43" s="147"/>
+      <c r="AR43" s="147"/>
+      <c r="AS43" s="147"/>
+      <c r="AT43" s="147"/>
+      <c r="AU43" s="147"/>
+      <c r="AV43" s="148"/>
+      <c r="AW43" s="148"/>
+      <c r="AX43" s="147"/>
+      <c r="AY43" s="147"/>
+      <c r="AZ43" s="147"/>
+      <c r="BA43" s="147"/>
+      <c r="BB43" s="147"/>
+      <c r="BC43" s="147"/>
+      <c r="BD43" s="147"/>
+      <c r="BE43" s="147"/>
+      <c r="BF43" s="147"/>
+      <c r="BG43" s="147"/>
+      <c r="BH43" s="147"/>
+      <c r="BI43" s="147"/>
+      <c r="BJ43" s="147"/>
+      <c r="BK43" s="149"/>
       <c r="BL43" s="9"/>
     </row>
     <row r="44" spans="1:87" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3593,44 +3593,44 @@
       <c r="J44" s="11"/>
       <c r="K44" s="11"/>
       <c r="L44" s="12"/>
-      <c r="M44" s="173"/>
-      <c r="N44" s="174"/>
-      <c r="O44" s="174"/>
-      <c r="P44" s="174"/>
-      <c r="Q44" s="174"/>
-      <c r="R44" s="174"/>
-      <c r="S44" s="174"/>
-      <c r="T44" s="174"/>
-      <c r="U44" s="174"/>
-      <c r="V44" s="174"/>
-      <c r="W44" s="174"/>
-      <c r="X44" s="174"/>
-      <c r="Y44" s="174"/>
-      <c r="Z44" s="174"/>
-      <c r="AA44" s="174"/>
-      <c r="AB44" s="174"/>
-      <c r="AC44" s="174"/>
-      <c r="AD44" s="174"/>
-      <c r="AE44" s="174"/>
-      <c r="AF44" s="174"/>
-      <c r="AG44" s="174"/>
-      <c r="AH44" s="174"/>
-      <c r="AI44" s="174"/>
-      <c r="AJ44" s="174"/>
-      <c r="AK44" s="174"/>
-      <c r="AL44" s="174"/>
-      <c r="AM44" s="174"/>
-      <c r="AN44" s="174"/>
-      <c r="AO44" s="175"/>
-      <c r="AP44" s="157"/>
-      <c r="AQ44" s="152" t="str">
+      <c r="M44" s="179"/>
+      <c r="N44" s="180"/>
+      <c r="O44" s="180"/>
+      <c r="P44" s="180"/>
+      <c r="Q44" s="180"/>
+      <c r="R44" s="180"/>
+      <c r="S44" s="180"/>
+      <c r="T44" s="180"/>
+      <c r="U44" s="180"/>
+      <c r="V44" s="180"/>
+      <c r="W44" s="180"/>
+      <c r="X44" s="180"/>
+      <c r="Y44" s="180"/>
+      <c r="Z44" s="180"/>
+      <c r="AA44" s="180"/>
+      <c r="AB44" s="180"/>
+      <c r="AC44" s="180"/>
+      <c r="AD44" s="180"/>
+      <c r="AE44" s="180"/>
+      <c r="AF44" s="180"/>
+      <c r="AG44" s="180"/>
+      <c r="AH44" s="180"/>
+      <c r="AI44" s="180"/>
+      <c r="AJ44" s="180"/>
+      <c r="AK44" s="180"/>
+      <c r="AL44" s="180"/>
+      <c r="AM44" s="180"/>
+      <c r="AN44" s="180"/>
+      <c r="AO44" s="181"/>
+      <c r="AP44" s="156"/>
+      <c r="AQ44" s="151" t="str">
         <f>$AQ$5</f>
         <v>Bagian</v>
       </c>
-      <c r="AR44" s="152"/>
-      <c r="AS44" s="152"/>
-      <c r="AT44" s="152"/>
-      <c r="AU44" s="152"/>
+      <c r="AR44" s="151"/>
+      <c r="AS44" s="151"/>
+      <c r="AT44" s="151"/>
+      <c r="AU44" s="151"/>
       <c r="AV44" s="128" t="str">
         <f>$AV$5</f>
         <v xml:space="preserve">:  </v>
@@ -3639,20 +3639,20 @@
         <f>$AW$5</f>
         <v>SectionName</v>
       </c>
-      <c r="AX44" s="152"/>
-      <c r="AY44" s="152"/>
-      <c r="AZ44" s="152"/>
-      <c r="BA44" s="152"/>
-      <c r="BB44" s="152"/>
-      <c r="BC44" s="152"/>
-      <c r="BD44" s="152"/>
-      <c r="BE44" s="152"/>
-      <c r="BF44" s="152"/>
-      <c r="BG44" s="152"/>
-      <c r="BH44" s="152"/>
-      <c r="BI44" s="152"/>
-      <c r="BJ44" s="152"/>
-      <c r="BK44" s="153"/>
+      <c r="AX44" s="151"/>
+      <c r="AY44" s="151"/>
+      <c r="AZ44" s="151"/>
+      <c r="BA44" s="151"/>
+      <c r="BB44" s="151"/>
+      <c r="BC44" s="151"/>
+      <c r="BD44" s="151"/>
+      <c r="BE44" s="151"/>
+      <c r="BF44" s="151"/>
+      <c r="BG44" s="151"/>
+      <c r="BH44" s="151"/>
+      <c r="BI44" s="151"/>
+      <c r="BJ44" s="151"/>
+      <c r="BK44" s="152"/>
       <c r="BL44" s="13"/>
     </row>
     <row r="45" spans="1:87" ht="6.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3724,74 +3724,74 @@
       <c r="BP46" s="22"/>
     </row>
     <row r="47" spans="1:87" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="182" t="s">
+      <c r="B47" s="185" t="s">
         <v>22</v>
       </c>
-      <c r="C47" s="183"/>
-      <c r="D47" s="183"/>
-      <c r="E47" s="183"/>
-      <c r="F47" s="183"/>
-      <c r="G47" s="183"/>
-      <c r="H47" s="183"/>
-      <c r="I47" s="183"/>
-      <c r="J47" s="183"/>
-      <c r="K47" s="183"/>
-      <c r="L47" s="183"/>
-      <c r="M47" s="183"/>
-      <c r="N47" s="183"/>
-      <c r="O47" s="183"/>
-      <c r="P47" s="183"/>
-      <c r="Q47" s="183"/>
-      <c r="R47" s="183"/>
-      <c r="S47" s="183"/>
-      <c r="T47" s="184"/>
+      <c r="C47" s="186"/>
+      <c r="D47" s="186"/>
+      <c r="E47" s="186"/>
+      <c r="F47" s="186"/>
+      <c r="G47" s="186"/>
+      <c r="H47" s="186"/>
+      <c r="I47" s="186"/>
+      <c r="J47" s="186"/>
+      <c r="K47" s="186"/>
+      <c r="L47" s="186"/>
+      <c r="M47" s="186"/>
+      <c r="N47" s="186"/>
+      <c r="O47" s="186"/>
+      <c r="P47" s="186"/>
+      <c r="Q47" s="186"/>
+      <c r="R47" s="186"/>
+      <c r="S47" s="186"/>
+      <c r="T47" s="187"/>
       <c r="U47" s="1"/>
-      <c r="V47" s="182" t="s">
+      <c r="V47" s="185" t="s">
         <v>23</v>
       </c>
-      <c r="W47" s="183"/>
-      <c r="X47" s="183"/>
-      <c r="Y47" s="183"/>
-      <c r="Z47" s="183"/>
-      <c r="AA47" s="183"/>
-      <c r="AB47" s="183"/>
-      <c r="AC47" s="183"/>
-      <c r="AD47" s="183"/>
-      <c r="AE47" s="183"/>
-      <c r="AF47" s="183"/>
-      <c r="AG47" s="183"/>
-      <c r="AH47" s="183"/>
-      <c r="AI47" s="183"/>
-      <c r="AJ47" s="183"/>
-      <c r="AK47" s="183"/>
-      <c r="AL47" s="183"/>
-      <c r="AM47" s="183"/>
-      <c r="AN47" s="183"/>
-      <c r="AO47" s="184"/>
+      <c r="W47" s="186"/>
+      <c r="X47" s="186"/>
+      <c r="Y47" s="186"/>
+      <c r="Z47" s="186"/>
+      <c r="AA47" s="186"/>
+      <c r="AB47" s="186"/>
+      <c r="AC47" s="186"/>
+      <c r="AD47" s="186"/>
+      <c r="AE47" s="186"/>
+      <c r="AF47" s="186"/>
+      <c r="AG47" s="186"/>
+      <c r="AH47" s="186"/>
+      <c r="AI47" s="186"/>
+      <c r="AJ47" s="186"/>
+      <c r="AK47" s="186"/>
+      <c r="AL47" s="186"/>
+      <c r="AM47" s="186"/>
+      <c r="AN47" s="186"/>
+      <c r="AO47" s="187"/>
       <c r="AP47" s="1"/>
-      <c r="AQ47" s="182" t="s">
+      <c r="AQ47" s="185" t="s">
         <v>24</v>
       </c>
-      <c r="AR47" s="183"/>
-      <c r="AS47" s="183"/>
-      <c r="AT47" s="183"/>
-      <c r="AU47" s="183"/>
-      <c r="AV47" s="183"/>
-      <c r="AW47" s="183"/>
-      <c r="AX47" s="183"/>
-      <c r="AY47" s="183"/>
-      <c r="AZ47" s="183"/>
-      <c r="BA47" s="183"/>
-      <c r="BB47" s="183"/>
-      <c r="BC47" s="183"/>
-      <c r="BD47" s="183"/>
-      <c r="BE47" s="183"/>
-      <c r="BF47" s="183"/>
-      <c r="BG47" s="183"/>
-      <c r="BH47" s="183"/>
-      <c r="BI47" s="183"/>
-      <c r="BJ47" s="183"/>
-      <c r="BK47" s="184"/>
+      <c r="AR47" s="186"/>
+      <c r="AS47" s="186"/>
+      <c r="AT47" s="186"/>
+      <c r="AU47" s="186"/>
+      <c r="AV47" s="186"/>
+      <c r="AW47" s="186"/>
+      <c r="AX47" s="186"/>
+      <c r="AY47" s="186"/>
+      <c r="AZ47" s="186"/>
+      <c r="BA47" s="186"/>
+      <c r="BB47" s="186"/>
+      <c r="BC47" s="186"/>
+      <c r="BD47" s="186"/>
+      <c r="BE47" s="186"/>
+      <c r="BF47" s="186"/>
+      <c r="BG47" s="186"/>
+      <c r="BH47" s="186"/>
+      <c r="BI47" s="186"/>
+      <c r="BJ47" s="186"/>
+      <c r="BK47" s="187"/>
       <c r="BN47" s="22"/>
       <c r="BO47" s="23"/>
       <c r="BP47" s="22"/>
@@ -3839,31 +3839,31 @@
       <c r="BI48" s="60"/>
       <c r="BJ48" s="56"/>
       <c r="BK48" s="75"/>
-      <c r="BO48" s="194"/>
-      <c r="BP48" s="194"/>
-      <c r="BQ48" s="194"/>
-      <c r="BR48" s="194"/>
-      <c r="BS48" s="194"/>
-      <c r="BT48" s="194"/>
-      <c r="BU48" s="194"/>
-      <c r="BV48" s="194"/>
-      <c r="BW48" s="194"/>
-      <c r="BX48" s="194"/>
-      <c r="BY48" s="194"/>
-      <c r="BZ48" s="194"/>
-      <c r="CA48" s="194"/>
-      <c r="CB48" s="194"/>
-      <c r="CC48" s="194"/>
-      <c r="CD48" s="194"/>
-      <c r="CE48" s="194"/>
-      <c r="CF48" s="194"/>
-      <c r="CG48" s="194"/>
-      <c r="CH48" s="194"/>
-      <c r="CI48" s="194"/>
+      <c r="BO48" s="169"/>
+      <c r="BP48" s="169"/>
+      <c r="BQ48" s="169"/>
+      <c r="BR48" s="169"/>
+      <c r="BS48" s="169"/>
+      <c r="BT48" s="169"/>
+      <c r="BU48" s="169"/>
+      <c r="BV48" s="169"/>
+      <c r="BW48" s="169"/>
+      <c r="BX48" s="169"/>
+      <c r="BY48" s="169"/>
+      <c r="BZ48" s="169"/>
+      <c r="CA48" s="169"/>
+      <c r="CB48" s="169"/>
+      <c r="CC48" s="169"/>
+      <c r="CD48" s="169"/>
+      <c r="CE48" s="169"/>
+      <c r="CF48" s="169"/>
+      <c r="CG48" s="169"/>
+      <c r="CH48" s="169"/>
+      <c r="CI48" s="169"/>
     </row>
     <row r="49" spans="2:84" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B49" s="161" t="s">
-        <v>51</v>
+      <c r="B49" s="160" t="s">
+        <v>50</v>
       </c>
       <c r="C49" s="122"/>
       <c r="D49" s="77"/>
@@ -3887,7 +3887,7 @@
         <v>1</v>
       </c>
       <c r="W49" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="X49" s="29"/>
       <c r="AO49" s="8"/>
@@ -4047,7 +4047,7 @@
       <c r="AO52" s="8"/>
       <c r="AQ52" s="88"/>
       <c r="AR52" s="80" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AS52" s="51"/>
       <c r="AT52" s="51"/>
@@ -4236,7 +4236,7 @@
         <v>4</v>
       </c>
       <c r="AR56" s="57" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AT56" s="95"/>
       <c r="AU56" s="95"/>
@@ -4382,23 +4382,23 @@
       <c r="BI59" s="95"/>
       <c r="BK59" s="8"/>
       <c r="BO59" s="1"/>
-      <c r="BP59" s="194"/>
-      <c r="BQ59" s="194"/>
-      <c r="BR59" s="194"/>
-      <c r="BS59" s="194"/>
-      <c r="BT59" s="194"/>
-      <c r="BU59" s="194"/>
-      <c r="BV59" s="194"/>
-      <c r="BW59" s="194"/>
-      <c r="BX59" s="194"/>
-      <c r="BY59" s="194"/>
-      <c r="BZ59" s="194"/>
-      <c r="CA59" s="194"/>
-      <c r="CB59" s="194"/>
-      <c r="CC59" s="194"/>
-      <c r="CD59" s="194"/>
-      <c r="CE59" s="194"/>
-      <c r="CF59" s="194"/>
+      <c r="BP59" s="169"/>
+      <c r="BQ59" s="169"/>
+      <c r="BR59" s="169"/>
+      <c r="BS59" s="169"/>
+      <c r="BT59" s="169"/>
+      <c r="BU59" s="169"/>
+      <c r="BV59" s="169"/>
+      <c r="BW59" s="169"/>
+      <c r="BX59" s="169"/>
+      <c r="BY59" s="169"/>
+      <c r="BZ59" s="169"/>
+      <c r="CA59" s="169"/>
+      <c r="CB59" s="169"/>
+      <c r="CC59" s="169"/>
+      <c r="CD59" s="169"/>
+      <c r="CE59" s="169"/>
+      <c r="CF59" s="169"/>
     </row>
     <row r="60" spans="2:84" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B60" s="98"/>
@@ -4496,28 +4496,28 @@
       <c r="R62" s="47"/>
       <c r="S62" s="47"/>
       <c r="T62" s="101"/>
-      <c r="V62" s="178" t="s">
+      <c r="V62" s="170" t="s">
         <v>31</v>
       </c>
-      <c r="W62" s="179"/>
-      <c r="X62" s="179"/>
-      <c r="Y62" s="179"/>
-      <c r="Z62" s="179"/>
-      <c r="AA62" s="179"/>
-      <c r="AB62" s="179"/>
-      <c r="AC62" s="179"/>
-      <c r="AD62" s="179"/>
-      <c r="AE62" s="179"/>
-      <c r="AF62" s="179"/>
-      <c r="AG62" s="179"/>
-      <c r="AH62" s="179"/>
-      <c r="AI62" s="179"/>
-      <c r="AJ62" s="179"/>
-      <c r="AK62" s="179"/>
-      <c r="AL62" s="179"/>
-      <c r="AM62" s="179"/>
-      <c r="AN62" s="179"/>
-      <c r="AO62" s="180"/>
+      <c r="W62" s="171"/>
+      <c r="X62" s="171"/>
+      <c r="Y62" s="171"/>
+      <c r="Z62" s="171"/>
+      <c r="AA62" s="171"/>
+      <c r="AB62" s="171"/>
+      <c r="AC62" s="171"/>
+      <c r="AD62" s="171"/>
+      <c r="AE62" s="171"/>
+      <c r="AF62" s="171"/>
+      <c r="AG62" s="171"/>
+      <c r="AH62" s="171"/>
+      <c r="AI62" s="171"/>
+      <c r="AJ62" s="171"/>
+      <c r="AK62" s="171"/>
+      <c r="AL62" s="171"/>
+      <c r="AM62" s="171"/>
+      <c r="AN62" s="171"/>
+      <c r="AO62" s="172"/>
       <c r="AP62" s="37"/>
       <c r="AS62" s="95"/>
       <c r="AT62" s="95"/>
@@ -4872,24 +4872,24 @@
       <c r="AO71" s="8"/>
       <c r="AP71" s="8"/>
       <c r="BK71" s="8"/>
-      <c r="BO71" s="194"/>
-      <c r="BP71" s="194"/>
-      <c r="BQ71" s="194"/>
-      <c r="BR71" s="194"/>
-      <c r="BS71" s="194"/>
-      <c r="BT71" s="194"/>
-      <c r="BU71" s="194"/>
-      <c r="BV71" s="194"/>
-      <c r="BW71" s="194"/>
-      <c r="BX71" s="194"/>
-      <c r="BY71" s="194"/>
-      <c r="BZ71" s="194"/>
-      <c r="CA71" s="194"/>
-      <c r="CB71" s="194"/>
-      <c r="CC71" s="194"/>
-      <c r="CD71" s="194"/>
-      <c r="CE71" s="194"/>
-      <c r="CF71" s="194"/>
+      <c r="BO71" s="169"/>
+      <c r="BP71" s="169"/>
+      <c r="BQ71" s="169"/>
+      <c r="BR71" s="169"/>
+      <c r="BS71" s="169"/>
+      <c r="BT71" s="169"/>
+      <c r="BU71" s="169"/>
+      <c r="BV71" s="169"/>
+      <c r="BW71" s="169"/>
+      <c r="BX71" s="169"/>
+      <c r="BY71" s="169"/>
+      <c r="BZ71" s="169"/>
+      <c r="CA71" s="169"/>
+      <c r="CB71" s="169"/>
+      <c r="CC71" s="169"/>
+      <c r="CD71" s="169"/>
+      <c r="CE71" s="169"/>
+      <c r="CF71" s="169"/>
     </row>
     <row r="72" spans="1:84" x14ac:dyDescent="0.2">
       <c r="B72" s="7"/>
@@ -4934,93 +4934,93 @@
       <c r="BK76" s="12"/>
     </row>
     <row r="77" spans="1:84" ht="14.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="178" t="s">
+      <c r="B77" s="170" t="s">
         <v>32</v>
       </c>
-      <c r="C77" s="179"/>
-      <c r="D77" s="179"/>
-      <c r="E77" s="179"/>
-      <c r="F77" s="179"/>
-      <c r="G77" s="179"/>
-      <c r="H77" s="179"/>
-      <c r="I77" s="179"/>
-      <c r="J77" s="179"/>
-      <c r="K77" s="179"/>
-      <c r="L77" s="179"/>
-      <c r="M77" s="179"/>
-      <c r="N77" s="179"/>
-      <c r="O77" s="179"/>
-      <c r="P77" s="179"/>
-      <c r="Q77" s="179"/>
-      <c r="R77" s="179"/>
-      <c r="S77" s="179"/>
-      <c r="T77" s="179"/>
-      <c r="U77" s="179"/>
-      <c r="V77" s="179"/>
-      <c r="W77" s="179"/>
-      <c r="X77" s="179"/>
-      <c r="Y77" s="179"/>
-      <c r="Z77" s="179"/>
-      <c r="AA77" s="179"/>
-      <c r="AB77" s="179"/>
-      <c r="AC77" s="179"/>
-      <c r="AD77" s="179"/>
-      <c r="AE77" s="179"/>
-      <c r="AF77" s="179"/>
-      <c r="AG77" s="179"/>
-      <c r="AH77" s="179"/>
-      <c r="AI77" s="179"/>
-      <c r="AJ77" s="179"/>
-      <c r="AK77" s="179"/>
-      <c r="AL77" s="179"/>
-      <c r="AM77" s="179"/>
-      <c r="AN77" s="179"/>
-      <c r="AO77" s="179"/>
-      <c r="AP77" s="179"/>
-      <c r="AQ77" s="179"/>
-      <c r="AR77" s="179"/>
-      <c r="AS77" s="179"/>
-      <c r="AT77" s="179"/>
-      <c r="AU77" s="179"/>
-      <c r="AV77" s="179"/>
-      <c r="AW77" s="179"/>
-      <c r="AX77" s="179"/>
-      <c r="AY77" s="179"/>
-      <c r="AZ77" s="179"/>
-      <c r="BA77" s="179"/>
-      <c r="BB77" s="179"/>
-      <c r="BC77" s="179"/>
-      <c r="BD77" s="179"/>
-      <c r="BE77" s="179"/>
-      <c r="BF77" s="179"/>
-      <c r="BG77" s="179"/>
-      <c r="BH77" s="179"/>
-      <c r="BI77" s="179"/>
-      <c r="BJ77" s="179"/>
-      <c r="BK77" s="180"/>
+      <c r="C77" s="171"/>
+      <c r="D77" s="171"/>
+      <c r="E77" s="171"/>
+      <c r="F77" s="171"/>
+      <c r="G77" s="171"/>
+      <c r="H77" s="171"/>
+      <c r="I77" s="171"/>
+      <c r="J77" s="171"/>
+      <c r="K77" s="171"/>
+      <c r="L77" s="171"/>
+      <c r="M77" s="171"/>
+      <c r="N77" s="171"/>
+      <c r="O77" s="171"/>
+      <c r="P77" s="171"/>
+      <c r="Q77" s="171"/>
+      <c r="R77" s="171"/>
+      <c r="S77" s="171"/>
+      <c r="T77" s="171"/>
+      <c r="U77" s="171"/>
+      <c r="V77" s="171"/>
+      <c r="W77" s="171"/>
+      <c r="X77" s="171"/>
+      <c r="Y77" s="171"/>
+      <c r="Z77" s="171"/>
+      <c r="AA77" s="171"/>
+      <c r="AB77" s="171"/>
+      <c r="AC77" s="171"/>
+      <c r="AD77" s="171"/>
+      <c r="AE77" s="171"/>
+      <c r="AF77" s="171"/>
+      <c r="AG77" s="171"/>
+      <c r="AH77" s="171"/>
+      <c r="AI77" s="171"/>
+      <c r="AJ77" s="171"/>
+      <c r="AK77" s="171"/>
+      <c r="AL77" s="171"/>
+      <c r="AM77" s="171"/>
+      <c r="AN77" s="171"/>
+      <c r="AO77" s="171"/>
+      <c r="AP77" s="171"/>
+      <c r="AQ77" s="171"/>
+      <c r="AR77" s="171"/>
+      <c r="AS77" s="171"/>
+      <c r="AT77" s="171"/>
+      <c r="AU77" s="171"/>
+      <c r="AV77" s="171"/>
+      <c r="AW77" s="171"/>
+      <c r="AX77" s="171"/>
+      <c r="AY77" s="171"/>
+      <c r="AZ77" s="171"/>
+      <c r="BA77" s="171"/>
+      <c r="BB77" s="171"/>
+      <c r="BC77" s="171"/>
+      <c r="BD77" s="171"/>
+      <c r="BE77" s="171"/>
+      <c r="BF77" s="171"/>
+      <c r="BG77" s="171"/>
+      <c r="BH77" s="171"/>
+      <c r="BI77" s="171"/>
+      <c r="BJ77" s="171"/>
+      <c r="BK77" s="172"/>
     </row>
     <row r="78" spans="1:84" ht="13.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="176" t="s">
+      <c r="B78" s="182" t="s">
         <v>33</v>
       </c>
-      <c r="C78" s="177"/>
-      <c r="D78" s="177"/>
-      <c r="E78" s="177"/>
-      <c r="F78" s="177"/>
-      <c r="G78" s="177"/>
-      <c r="H78" s="177"/>
-      <c r="I78" s="177"/>
-      <c r="J78" s="177"/>
-      <c r="K78" s="177"/>
-      <c r="L78" s="177"/>
-      <c r="M78" s="177"/>
-      <c r="N78" s="177"/>
-      <c r="O78" s="177"/>
-      <c r="P78" s="177"/>
-      <c r="Q78" s="177"/>
-      <c r="R78" s="177"/>
-      <c r="S78" s="177"/>
-      <c r="T78" s="177"/>
+      <c r="C78" s="183"/>
+      <c r="D78" s="183"/>
+      <c r="E78" s="183"/>
+      <c r="F78" s="183"/>
+      <c r="G78" s="183"/>
+      <c r="H78" s="183"/>
+      <c r="I78" s="183"/>
+      <c r="J78" s="183"/>
+      <c r="K78" s="183"/>
+      <c r="L78" s="183"/>
+      <c r="M78" s="183"/>
+      <c r="N78" s="183"/>
+      <c r="O78" s="183"/>
+      <c r="P78" s="183"/>
+      <c r="Q78" s="183"/>
+      <c r="R78" s="183"/>
+      <c r="S78" s="183"/>
+      <c r="T78" s="183"/>
       <c r="U78" s="4"/>
       <c r="V78" s="108" t="s">
         <v>34</v>
@@ -5052,7 +5052,7 @@
       <c r="S79" s="47"/>
       <c r="T79" s="47"/>
       <c r="V79" s="47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="W79" s="47"/>
       <c r="AQ79" s="110" t="s">
@@ -5102,12 +5102,10 @@
     </row>
     <row r="81" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A81" s="56"/>
-      <c r="B81" s="164" t="s">
-        <v>53</v>
-      </c>
-      <c r="C81" s="33" t="s">
-        <v>46</v>
-      </c>
+      <c r="B81" s="197" t="s">
+        <v>45</v>
+      </c>
+      <c r="C81" s="56"/>
       <c r="D81" s="56"/>
       <c r="E81" s="112"/>
       <c r="F81" s="112"/>
@@ -5126,12 +5124,10 @@
       <c r="S81" s="112"/>
       <c r="T81" s="112"/>
       <c r="U81" s="56"/>
-      <c r="V81" s="135" t="s">
-        <v>53</v>
-      </c>
-      <c r="W81" s="137" t="s">
-        <v>54</v>
-      </c>
+      <c r="V81" s="136" t="s">
+        <v>52</v>
+      </c>
+      <c r="W81" s="56"/>
       <c r="X81" s="56"/>
       <c r="Y81" s="56"/>
       <c r="Z81" s="56"/>
@@ -5151,24 +5147,18 @@
       <c r="AN81" s="56"/>
       <c r="AO81" s="56"/>
       <c r="AP81" s="56"/>
-      <c r="AQ81" s="135" t="s">
+      <c r="AQ81" s="198" t="s">
         <v>53</v>
       </c>
-      <c r="AR81" s="158" t="s">
-        <v>39</v>
-      </c>
+      <c r="AR81" s="157"/>
       <c r="AS81" s="56"/>
       <c r="AT81" s="56"/>
       <c r="BK81" s="8"/>
     </row>
     <row r="82" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A82" s="56"/>
-      <c r="B82" s="165" t="s">
-        <v>55</v>
-      </c>
-      <c r="C82" s="33" t="s">
-        <v>39</v>
-      </c>
+      <c r="B82" s="164"/>
+      <c r="C82" s="33"/>
       <c r="D82" s="112"/>
       <c r="E82" s="112"/>
       <c r="F82" s="112"/>
@@ -5187,12 +5177,8 @@
       <c r="S82" s="112"/>
       <c r="T82" s="112"/>
       <c r="U82" s="56"/>
-      <c r="V82" s="135" t="s">
-        <v>55</v>
-      </c>
-      <c r="W82" s="166" t="s">
-        <v>39</v>
-      </c>
+      <c r="V82" s="135"/>
+      <c r="W82" s="165"/>
       <c r="X82" s="56"/>
       <c r="Y82" s="56"/>
       <c r="Z82" s="56"/>
@@ -5212,24 +5198,16 @@
       <c r="AN82" s="56"/>
       <c r="AO82" s="56"/>
       <c r="AP82" s="56"/>
-      <c r="AQ82" s="135" t="s">
-        <v>55</v>
-      </c>
-      <c r="AR82" s="158" t="s">
-        <v>39</v>
-      </c>
+      <c r="AQ82" s="135"/>
+      <c r="AR82" s="157"/>
       <c r="AS82" s="56"/>
       <c r="AT82" s="56"/>
       <c r="BK82" s="8"/>
     </row>
     <row r="83" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A83" s="56"/>
-      <c r="B83" s="164" t="s">
-        <v>56</v>
-      </c>
-      <c r="C83" s="159" t="s">
-        <v>39</v>
-      </c>
+      <c r="B83" s="163"/>
+      <c r="C83" s="158"/>
       <c r="D83" s="112"/>
       <c r="E83" s="112"/>
       <c r="F83" s="112"/>
@@ -5248,12 +5226,8 @@
       <c r="S83" s="112"/>
       <c r="T83" s="112"/>
       <c r="U83" s="56"/>
-      <c r="V83" s="113" t="s">
-        <v>56</v>
-      </c>
-      <c r="W83" s="166" t="s">
-        <v>39</v>
-      </c>
+      <c r="V83" s="113"/>
+      <c r="W83" s="165"/>
       <c r="X83" s="56"/>
       <c r="Y83" s="56"/>
       <c r="Z83" s="56"/>
@@ -5273,20 +5247,16 @@
       <c r="AN83" s="56"/>
       <c r="AO83" s="56"/>
       <c r="AP83" s="56"/>
-      <c r="AQ83" s="113" t="s">
-        <v>56</v>
-      </c>
-      <c r="AR83" s="158" t="s">
-        <v>39</v>
-      </c>
+      <c r="AQ83" s="113"/>
+      <c r="AR83" s="157"/>
       <c r="AS83" s="56"/>
       <c r="AT83" s="56"/>
       <c r="BK83" s="8"/>
     </row>
     <row r="84" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A84" s="56"/>
-      <c r="B84" s="164"/>
-      <c r="C84" s="159"/>
+      <c r="B84" s="163"/>
+      <c r="C84" s="158"/>
       <c r="D84" s="112"/>
       <c r="E84" s="112"/>
       <c r="F84" s="112"/>
@@ -5305,7 +5275,7 @@
       <c r="S84" s="112"/>
       <c r="T84" s="112"/>
       <c r="U84" s="56"/>
-      <c r="V84" s="137"/>
+      <c r="V84" s="136"/>
       <c r="W84" s="56"/>
       <c r="X84" s="56"/>
       <c r="Y84" s="56"/>
@@ -5326,7 +5296,7 @@
       <c r="AN84" s="56"/>
       <c r="AO84" s="56"/>
       <c r="AP84" s="56"/>
-      <c r="AQ84" s="137"/>
+      <c r="AQ84" s="136"/>
       <c r="AR84" s="56"/>
       <c r="AS84" s="56"/>
       <c r="AT84" s="56"/>
@@ -5334,8 +5304,8 @@
     </row>
     <row r="85" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A85" s="56"/>
-      <c r="B85" s="115"/>
-      <c r="C85" s="136"/>
+      <c r="B85" s="199"/>
+      <c r="C85" s="158"/>
       <c r="D85" s="112"/>
       <c r="E85" s="112"/>
       <c r="F85" s="112"/>
@@ -5354,7 +5324,7 @@
       <c r="S85" s="112"/>
       <c r="T85" s="112"/>
       <c r="U85" s="56"/>
-      <c r="V85" s="138"/>
+      <c r="V85" s="137"/>
       <c r="W85" s="33"/>
       <c r="X85" s="56"/>
       <c r="Y85" s="56"/>
@@ -5365,15 +5335,26 @@
       <c r="AD85" s="56"/>
       <c r="AE85" s="56"/>
       <c r="AF85" s="56"/>
-      <c r="AP85" s="22"/>
-      <c r="AQ85" s="9"/>
+      <c r="AG85" s="56"/>
+      <c r="AH85" s="56"/>
+      <c r="AI85" s="56"/>
+      <c r="AJ85" s="56"/>
+      <c r="AK85" s="56"/>
+      <c r="AL85" s="56"/>
+      <c r="AM85" s="56"/>
+      <c r="AN85" s="56"/>
+      <c r="AO85" s="56"/>
+      <c r="AP85" s="49"/>
+      <c r="AQ85" s="56"/>
+      <c r="AR85" s="56"/>
+      <c r="AS85" s="56"/>
       <c r="AX85" s="116"/>
       <c r="BK85" s="8"/>
     </row>
     <row r="86" spans="1:63" x14ac:dyDescent="0.25">
       <c r="A86" s="56"/>
       <c r="B86" s="115"/>
-      <c r="C86" s="136"/>
+      <c r="C86" s="158"/>
       <c r="D86" s="112"/>
       <c r="E86" s="112"/>
       <c r="F86" s="112"/>
@@ -5392,7 +5373,7 @@
       <c r="S86" s="112"/>
       <c r="T86" s="112"/>
       <c r="U86" s="56"/>
-      <c r="V86" s="138"/>
+      <c r="V86" s="137"/>
       <c r="W86" s="33"/>
       <c r="X86" s="56"/>
       <c r="Y86" s="56"/>
@@ -5403,39 +5384,50 @@
       <c r="AD86" s="56"/>
       <c r="AE86" s="56"/>
       <c r="AF86" s="56"/>
-      <c r="AP86" s="22"/>
-      <c r="AQ86" s="9"/>
+      <c r="AG86" s="56"/>
+      <c r="AH86" s="56"/>
+      <c r="AI86" s="56"/>
+      <c r="AJ86" s="56"/>
+      <c r="AK86" s="56"/>
+      <c r="AL86" s="56"/>
+      <c r="AM86" s="56"/>
+      <c r="AN86" s="56"/>
+      <c r="AO86" s="56"/>
+      <c r="AP86" s="49"/>
+      <c r="AQ86" s="200"/>
+      <c r="AR86" s="56"/>
+      <c r="AS86" s="56"/>
       <c r="AX86" s="116"/>
       <c r="BK86" s="8"/>
     </row>
     <row r="87" spans="1:63" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A87" s="56"/>
-      <c r="B87" s="139"/>
+      <c r="B87" s="138"/>
       <c r="C87" s="128"/>
-      <c r="D87" s="140"/>
-      <c r="E87" s="140"/>
-      <c r="F87" s="140"/>
-      <c r="G87" s="140"/>
-      <c r="H87" s="140"/>
-      <c r="I87" s="140"/>
-      <c r="J87" s="140"/>
-      <c r="K87" s="140"/>
-      <c r="L87" s="140"/>
-      <c r="M87" s="140"/>
-      <c r="N87" s="140"/>
-      <c r="O87" s="140"/>
-      <c r="P87" s="140"/>
-      <c r="Q87" s="140"/>
-      <c r="R87" s="140"/>
-      <c r="S87" s="140"/>
-      <c r="T87" s="140"/>
+      <c r="D87" s="139"/>
+      <c r="E87" s="139"/>
+      <c r="F87" s="139"/>
+      <c r="G87" s="139"/>
+      <c r="H87" s="139"/>
+      <c r="I87" s="139"/>
+      <c r="J87" s="139"/>
+      <c r="K87" s="139"/>
+      <c r="L87" s="139"/>
+      <c r="M87" s="139"/>
+      <c r="N87" s="139"/>
+      <c r="O87" s="139"/>
+      <c r="P87" s="139"/>
+      <c r="Q87" s="139"/>
+      <c r="R87" s="139"/>
+      <c r="S87" s="139"/>
+      <c r="T87" s="139"/>
       <c r="U87" s="128"/>
       <c r="V87" s="128"/>
       <c r="W87" s="65"/>
       <c r="X87" s="128"/>
       <c r="Y87" s="128"/>
       <c r="Z87" s="128"/>
-      <c r="AA87" s="140"/>
+      <c r="AA87" s="139"/>
       <c r="AB87" s="128"/>
       <c r="AC87" s="128"/>
       <c r="AD87" s="128"/>
@@ -5529,11 +5521,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="BO48:CI48"/>
-    <mergeCell ref="BP59:CF59"/>
-    <mergeCell ref="V62:AO62"/>
-    <mergeCell ref="BO71:CF71"/>
-    <mergeCell ref="B77:BK77"/>
     <mergeCell ref="M2:AO5"/>
     <mergeCell ref="B78:T78"/>
     <mergeCell ref="B23:BK23"/>
@@ -5547,6 +5534,11 @@
     <mergeCell ref="X8:AO8"/>
     <mergeCell ref="AQ8:BK8"/>
     <mergeCell ref="X9:AO11"/>
+    <mergeCell ref="BO48:CI48"/>
+    <mergeCell ref="BP59:CF59"/>
+    <mergeCell ref="V62:AO62"/>
+    <mergeCell ref="BO71:CF71"/>
+    <mergeCell ref="B77:BK77"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0.19685039370078741" header="3.937007874015748E-2" footer="0.23622047244094491"/>
